--- a/products/shared/Client-Finder-CRM.xlsx
+++ b/products/shared/Client-Finder-CRM.xlsx
@@ -110,7 +110,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="1"/>
@@ -180,6 +180,16 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FEE2E2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -777,18 +787,24 @@
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="6">
       <formula>"Do not contact"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="6">
+      <formula>"Not interested"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="7">
+      <formula>"Bounced"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
       <formula>"Draft ready"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K5000">
-    <cfRule type="expression" priority="10" dxfId="8">
+    <cfRule type="expression" priority="12" dxfId="9">
       <formula>K2&gt;=60</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="T2:T5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a status from the list" prompt="New → Draft ready / Pitch ready → Contacted → Replied → Meeting booked → Won / Lost" type="list">
-      <formula1>"New,Pitch ready,Draft ready,Contacted,Follow-up drafted,Replied,Meeting booked,Won,Lost,Do not contact"</formula1>
+      <formula1>"New,Pitch ready,Draft ready,Contacted,Follow-up drafted,Replied,Meeting booked,Won,Lost,Do not contact,Not interested,Bounced"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -801,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -945,83 +961,105 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Not interested</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>COUNTIF(Leads!T:T,"Not interested")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bounced</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>COUNTIF(Leads!T:T,"Bounced")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B17">
         <f>COUNTA(Leads!A:A)-1</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Leads</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="B18">
-        <f>COUNTIF(Leads!L:L,"Hot")</f>
-        <v/>
-      </c>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="B19">
-        <f>COUNTIF(Leads!L:L,"Warm")</f>
-        <v/>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="B20">
-        <f>COUNTIF(Leads!L:L,"Low")</f>
+        <f>COUNTIF(Leads!L:L,"Hot")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Warm</t>
         </is>
       </c>
       <c r="B21">
-        <f>COUNTIF(Leads!L:L,"None")</f>
+        <f>COUNTIF(Leads!L:L,"Warm")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>COUNTIF(Leads!L:L,"Low")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>COUNTIF(Leads!L:L,"None")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Reply rate</t>
         </is>
       </c>
-      <c r="B23" s="6">
+      <c r="B25" s="6">
         <f>IFERROR((COUNTIF(Leads!T:T,"Replied")+COUNTIF(Leads!T:T,"Meeting booked")+COUNTIF(Leads!T:T,"Won"))/MAX(1,COUNTIF(Leads!T:T,"Contacted")+COUNTIF(Leads!T:T,"Follow-up drafted")+COUNTIF(Leads!T:T,"Replied")+COUNTIF(Leads!T:T,"Meeting booked")+COUNTIF(Leads!T:T,"Won")+COUNTIF(Leads!T:T,"Lost")),0)</f>
         <v/>
       </c>
@@ -1037,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1067,35 +1105,35 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>3. Every run adds new businesses at the bottom. A business that is already in the sheet is never added or pitched twice.</t>
+          <t>3. Every run adds new businesses at the bottom. A business that is already in the sheet is never added twice, and an email address or website that is already here is never pitched again.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>4. Statuses: New = no pitch (score too low) · Pitch ready = pitch written, no email found (call/DM) · Draft ready = a Gmail draft is waiting for you.</t>
+          <t>4. Statuses: New = no pitch (score too low, or already pitched under another listing) · Pitch ready = pitch written, no email found or the draft failed (call/DM) · Draft ready = a Gmail draft is waiting for you.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   After you send: Contacted · Follow-up drafted (Pro) · Replied · Meeting booked · Won · Lost · Do not contact.</t>
+          <t xml:space="preserve">   After you send: Contacted · Follow-up drafted (Pro) · Replied · Meeting booked · Won · Lost · Do not contact · Not interested · Bounced (Pro sets it when an email bounces).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5. Pro follow-ups read Gmail to see what you actually sent and who replied. You can also set Status and Last Contacted by hand.</t>
+          <t>5. Pro follow-ups read Gmail to see what you actually sent and who replied (from any address in the thread). You can also set Status and Last Contacted by hand.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>6. Set Status to "Do not contact" for anyone who asks you to stop. They are never emailed again.</t>
+          <t>6. Set Status to "Do not contact" (or "Not interested") for anyone who asks you to stop. That email address and website are never emailed or pitched again, even from another row.</t>
         </is>
       </c>
     </row>
@@ -1103,6 +1141,13 @@
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>7. Add your own columns to the right of Notes if you like: the workflows ignore them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>8. Business details come from Google Maps (source: Google Maps). Google's Maps Platform Terms limit storing them long term, so treat this tab as a working list and delete leads you don't pursue.</t>
         </is>
       </c>
     </row>

--- a/products/shared/Client-Finder-CRM.xlsx
+++ b/products/shared/Client-Finder-CRM.xlsx
@@ -1133,7 +1133,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>6. Set Status to "Do not contact" (or "Not interested") for anyone who asks you to stop. That email address and website are never emailed or pitched again, even from another row.</t>
+          <t>6. Set Status to "Do not contact" (or "Not interested") for anyone who asks you to stop. That email address is never emailed again by any workflow, and the Client Finder never pitches that address or website again, even under another listing.</t>
         </is>
       </c>
     </row>

--- a/products/shared/Client-Finder-CRM.xlsx
+++ b/products/shared/Client-Finder-CRM.xlsx
@@ -1126,7 +1126,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5. Pro follow-ups read Gmail to see what you actually sent and who replied (from any address in the thread). You can also set Status and Last Contacted by hand.</t>
+          <t>5. Pro follow-ups read Gmail to see what you actually sent and who replied (from any address in the thread). You can also set Status and Last Contacted by hand; a status that isn't in the list means hands off.</t>
         </is>
       </c>
     </row>
